--- a/colombres/colombres 360.xlsx
+++ b/colombres/colombres 360.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\colombres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1185B3F-3AA0-408E-90F0-925C5358B281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258375C0-D4B8-4C63-87FF-A2705AF82F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="175">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -150,9 +150,6 @@
     <t>GASTOS EXTRAORDINARIOS UNIDADES FUNCIONALES:</t>
   </si>
   <si>
-    <t>PREVISION ORDINARIA</t>
-  </si>
-  <si>
     <t>PREVISION EXTRAORDINARIA</t>
   </si>
   <si>
@@ -313,9 +310,6 @@
   </si>
   <si>
     <t>162450.31</t>
-  </si>
-  <si>
-    <t>Punitorios mal cobrados</t>
   </si>
   <si>
     <t>SCABUZZO ANA MARIA</t>
@@ -486,9 +480,6 @@
     <t>Banco Supervielle - Mantenimiento cuenta corriente</t>
   </si>
   <si>
-    <t>Transf 01/07</t>
-  </si>
-  <si>
     <t xml:space="preserve">AySA - Cuenta 1266646 </t>
   </si>
   <si>
@@ -504,9 +495,6 @@
     <t>Transf 14/07</t>
   </si>
   <si>
-    <t>SAC - Neto</t>
-  </si>
-  <si>
     <t>Transf 29/07</t>
   </si>
   <si>
@@ -519,12 +507,6 @@
     <t>Transf 08/07</t>
   </si>
   <si>
-    <t xml:space="preserve">Honorarios administracion anterior </t>
-  </si>
-  <si>
-    <t>Transf 11/07</t>
-  </si>
-  <si>
     <t>Sasa - Servicio de confeccion y liquidacion de datos - Junio 2025 - Administracion anterior</t>
   </si>
   <si>
@@ -552,18 +534,44 @@
     <t>Deposito en efectivo 11/07</t>
   </si>
   <si>
-    <t>Transf no identificada - Mozart Srl - 11/07</t>
+    <t>Punitorios mal cobrados por administracion saliente</t>
+  </si>
+  <si>
+    <t>Mozart Srl</t>
+  </si>
+  <si>
+    <t>SAC neto</t>
+  </si>
+  <si>
+    <t>Transf 03/07</t>
+  </si>
+  <si>
+    <t>Honorarios administracion anterior</t>
+  </si>
+  <si>
+    <t>Transf 15/07</t>
+  </si>
+  <si>
+    <t>MES QUE VIENE (EN AGOST0 QUEDA PENDIENTE AGREGAR EL TRASPASO DE ADMINISTRACION QUE ES DE $180MIL PESOS</t>
+  </si>
+  <si>
+    <t>Devolucion anticipo SAC mes pasado (Gestionado por administracion saliente)</t>
+  </si>
+  <si>
+    <t>PREVISION ORDINARIA - ARREGLOS DE ASCENSOR QUE SE HICIERON - BOMBAS (QUE SE DEBEN ABONAR EN LOS PRIMEROS DIAS)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="6">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -823,7 +831,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1152,13 +1160,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1289,7 +1310,6 @@
     <xf numFmtId="165" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1302,9 +1322,6 @@
     </xf>
     <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1339,12 +1356,38 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1354,17 +1397,65 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1378,96 +1469,28 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="20" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="20" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1836,58 +1859,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="174" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="130"/>
+      <c r="A1" s="136" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="128"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="131" t="s">
-        <v>128</v>
-      </c>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
+      <c r="A2" s="129" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
     </row>
     <row r="3" spans="1:4" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="131" t="s">
+      <c r="A3" s="129" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+    </row>
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="145" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="131"/>
-      <c r="C3" s="131"/>
-      <c r="D3" s="131"/>
-    </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="175" t="s">
-        <v>129</v>
-      </c>
-      <c r="B4" s="175"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="132"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="175"/>
-      <c r="B5" s="175"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132"/>
+      <c r="A5" s="145"/>
+      <c r="B5" s="145"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="175"/>
-      <c r="B6" s="175"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="132"/>
+      <c r="A6" s="145"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="130"/>
+      <c r="D6" s="130"/>
     </row>
     <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="175"/>
-      <c r="B7" s="175"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
+      <c r="A7" s="145"/>
+      <c r="B7" s="145"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="130"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9" s="142" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1898,30 +1921,30 @@
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="176" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="176"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="176"/>
+      <c r="A14" s="141" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="141"/>
+      <c r="C14" s="141"/>
+      <c r="D14" s="141"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="176"/>
-      <c r="B15" s="176"/>
-      <c r="C15" s="176"/>
-      <c r="D15" s="176"/>
+      <c r="A15" s="141"/>
+      <c r="B15" s="141"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="141"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="176"/>
-      <c r="B16" s="176"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="176"/>
+      <c r="A16" s="141"/>
+      <c r="B16" s="141"/>
+      <c r="C16" s="141"/>
+      <c r="D16" s="141"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="176"/>
-      <c r="B17" s="176"/>
-      <c r="C17" s="176"/>
-      <c r="D17" s="176"/>
+      <c r="A17" s="141"/>
+      <c r="B17" s="141"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="141"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1938,7 +1961,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="25"/>
@@ -1946,161 +1969,155 @@
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B23" s="5"/>
-      <c r="C23" s="124">
-        <v>1418273.25</v>
+      <c r="C23" s="122">
+        <v>1144385.8999999999</v>
       </c>
       <c r="D23" s="84"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="124">
-        <v>-308474.25</v>
+      <c r="C24" s="122">
+        <v>-466337.9</v>
       </c>
       <c r="D24" s="84"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="124">
-        <v>0</v>
-      </c>
+      <c r="C25" s="122"/>
       <c r="D25" s="84"/>
       <c r="G25" s="14"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B26" s="5"/>
-      <c r="C26" s="124">
-        <v>690667</v>
+      <c r="C26" s="122">
+        <v>470408</v>
       </c>
       <c r="D26" s="84"/>
       <c r="G26" s="14"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27" s="50"/>
-      <c r="C27" s="125">
+      <c r="C27" s="123">
         <f>SUM(C23:C26)</f>
-        <v>1800466</v>
+        <v>1148456</v>
       </c>
       <c r="D27" s="85"/>
-      <c r="G27" s="126"/>
+      <c r="G27" s="124"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>141</v>
+      <c r="A28" s="135" t="s">
+        <v>140</v>
       </c>
       <c r="B28" s="5"/>
-      <c r="C28" s="124">
-        <v>1418273.25</v>
+      <c r="C28" s="122">
+        <v>1005541.03</v>
       </c>
       <c r="D28" s="84"/>
-      <c r="G28" s="126"/>
+      <c r="G28" s="124"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="120">
-        <v>-308474.25</v>
+      <c r="C29" s="118">
+        <v>-218705.03</v>
       </c>
       <c r="D29" s="84"/>
       <c r="G29" s="14"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="120">
-        <v>0</v>
-      </c>
+      <c r="C30" s="118"/>
       <c r="D30" s="84"/>
       <c r="G30" s="14"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B31" s="5"/>
-      <c r="C31" s="120">
-        <v>690667</v>
+      <c r="C31" s="118">
+        <v>526597</v>
       </c>
       <c r="D31" s="84"/>
       <c r="G31" s="14"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B32" s="50"/>
       <c r="C32" s="51">
         <f>SUM(C28:C31)</f>
-        <v>1800466</v>
+        <v>1313433</v>
       </c>
       <c r="D32" s="85"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="173" t="s">
-        <v>142</v>
-      </c>
-      <c r="B33" s="170"/>
-      <c r="C33" s="124">
-        <v>1005541.03</v>
-      </c>
-      <c r="D33" s="172"/>
+      <c r="A33" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="122">
+        <v>1418273.25</v>
+      </c>
+      <c r="D33" s="134"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B34" s="170"/>
-      <c r="C34" s="124">
-        <v>-218705.03</v>
-      </c>
-      <c r="D34" s="172"/>
+        <v>81</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="122">
+        <v>-308474.25</v>
+      </c>
+      <c r="D34" s="134"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B35" s="170"/>
-      <c r="C35" s="124">
-        <v>0</v>
-      </c>
-      <c r="D35" s="172"/>
+        <v>83</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="122"/>
+      <c r="D35" s="134"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B36" s="182"/>
-      <c r="C36" s="120">
-        <v>526597</v>
-      </c>
-      <c r="D36" s="172"/>
+        <v>168</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="118">
+        <v>690667</v>
+      </c>
+      <c r="D36" s="134"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="B37" s="171"/>
+        <v>82</v>
+      </c>
+      <c r="B37" s="133"/>
       <c r="C37" s="51">
         <f>SUM(C33:C36)</f>
-        <v>1313433</v>
+        <v>1800466</v>
       </c>
       <c r="D37" s="85"/>
     </row>
@@ -2112,7 +2129,7 @@
       <c r="C38" s="20"/>
       <c r="D38" s="86">
         <f>C27+C32+C37</f>
-        <v>4914365</v>
+        <v>4262355</v>
       </c>
       <c r="E38" s="14"/>
       <c r="F38" s="14"/>
@@ -2131,31 +2148,33 @@
         <v>39</v>
       </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="124"/>
+      <c r="C40" s="122"/>
       <c r="D40" s="88"/>
       <c r="G40" s="14"/>
     </row>
     <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="180" t="s">
-        <v>143</v>
-      </c>
-      <c r="B41" s="129"/>
-      <c r="C41" s="124"/>
+      <c r="A41" s="137" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" s="127"/>
+      <c r="C41" s="122"/>
       <c r="D41" s="88"/>
       <c r="G41" s="14"/>
     </row>
-    <row r="42" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="180" t="s">
-        <v>161</v>
-      </c>
-      <c r="B42" s="129"/>
-      <c r="C42" s="179">
+    <row r="42" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="137" t="s">
+        <v>170</v>
+      </c>
+      <c r="B42" s="127"/>
+      <c r="C42" s="122">
         <v>392500</v>
       </c>
-      <c r="D42" s="88" t="s">
-        <v>162</v>
-      </c>
-      <c r="G42" s="14"/>
+      <c r="D42" s="175" t="s">
+        <v>171</v>
+      </c>
+      <c r="G42" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="18" t="s">
@@ -2170,34 +2189,34 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B44" s="26"/>
       <c r="C44" s="29"/>
       <c r="D44" s="61"/>
     </row>
     <row r="45" spans="1:7" s="35" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="134" t="s">
-        <v>138</v>
-      </c>
-      <c r="B45" s="135"/>
-      <c r="C45" s="168">
+      <c r="A45" s="143" t="s">
+        <v>136</v>
+      </c>
+      <c r="B45" s="144"/>
+      <c r="C45" s="181">
         <v>175052</v>
       </c>
-      <c r="D45" s="114" t="s">
-        <v>154</v>
+      <c r="D45" s="112" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="134" t="s">
-        <v>139</v>
-      </c>
-      <c r="B46" s="135"/>
-      <c r="C46" s="169">
-        <v>4206</v>
-      </c>
-      <c r="D46" s="114" t="s">
-        <v>152</v>
+      <c r="A46" s="143" t="s">
+        <v>137</v>
+      </c>
+      <c r="B46" s="144"/>
+      <c r="C46" s="182">
+        <v>4203</v>
+      </c>
+      <c r="D46" s="112" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2208,7 +2227,7 @@
       <c r="C47" s="32"/>
       <c r="D47" s="90">
         <f>SUM(C45:C46)</f>
-        <v>179258</v>
+        <v>179255</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -2221,51 +2240,51 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B49" s="5"/>
-      <c r="C49" s="181">
+      <c r="C49" s="31">
         <v>2530143.65</v>
       </c>
-      <c r="D49" s="121" t="s">
-        <v>153</v>
-      </c>
-      <c r="F49" s="183"/>
+      <c r="D49" s="119" t="s">
+        <v>150</v>
+      </c>
+      <c r="F49" s="138"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B50" s="5"/>
-      <c r="C50" s="178">
+      <c r="C50" s="111">
         <v>29588.720000000001</v>
       </c>
-      <c r="D50" s="121" t="s">
-        <v>153</v>
+      <c r="D50" s="119" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B51" s="5"/>
-      <c r="C51" s="178">
+      <c r="C51" s="111">
         <v>266298.44</v>
       </c>
-      <c r="D51" s="121" t="str">
+      <c r="D51" s="119" t="str">
         <f>D50</f>
         <v>Debito 14/07</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B52" s="5"/>
-      <c r="C52" s="178">
+      <c r="C52" s="111">
         <v>493841.29</v>
       </c>
-      <c r="D52" s="122" t="str">
+      <c r="D52" s="120" t="str">
         <f>D51</f>
         <v>Debito 14/07</v>
       </c>
@@ -2291,54 +2310,54 @@
     </row>
     <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B55" s="5"/>
-      <c r="C55" s="178">
+      <c r="C55" s="111">
         <v>529265.89</v>
       </c>
       <c r="D55" s="96" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B56" s="5"/>
-      <c r="C56" s="178">
+      <c r="C56" s="111">
         <v>54600.160000000003</v>
       </c>
-      <c r="D56" s="122" t="s">
-        <v>155</v>
+      <c r="D56" s="120" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B57" s="5"/>
-      <c r="C57" s="178">
+      <c r="C57" s="111">
         <v>727695.66</v>
       </c>
       <c r="D57" s="96" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="159" t="s">
-        <v>133</v>
-      </c>
-      <c r="B58" s="160"/>
-      <c r="C58" s="112"/>
+      <c r="A58" s="149" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="150"/>
+      <c r="C58" s="111"/>
       <c r="D58" s="96"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B59" s="128"/>
-      <c r="C59" s="112"/>
+        <v>130</v>
+      </c>
+      <c r="B59" s="126"/>
+      <c r="C59" s="111"/>
       <c r="D59" s="96"/>
     </row>
     <row r="60" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2361,78 +2380,78 @@
       <c r="D61" s="94"/>
     </row>
     <row r="62" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="161" t="s">
+      <c r="A62" s="151" t="s">
+        <v>132</v>
+      </c>
+      <c r="B62" s="152"/>
+      <c r="C62" s="111"/>
+      <c r="D62" s="115"/>
+    </row>
+    <row r="63" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="151" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" s="152"/>
+      <c r="C63" s="111"/>
+      <c r="D63" s="114"/>
+    </row>
+    <row r="64" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="153" t="s">
         <v>134</v>
       </c>
-      <c r="B62" s="162"/>
-      <c r="C62" s="112"/>
-      <c r="D62" s="117"/>
-    </row>
-    <row r="63" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="163" t="s">
-        <v>135</v>
-      </c>
-      <c r="B63" s="164"/>
-      <c r="C63" s="112"/>
-      <c r="D63" s="116"/>
-    </row>
-    <row r="64" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="165" t="s">
-        <v>136</v>
-      </c>
-      <c r="B64" s="166"/>
+      <c r="B64" s="154"/>
       <c r="C64" s="31"/>
       <c r="D64" s="93"/>
     </row>
-    <row r="65" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="139" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" s="140"/>
+      <c r="C65" s="31">
+        <v>250000</v>
+      </c>
+      <c r="D65" s="132" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="139" t="s">
+        <v>157</v>
+      </c>
+      <c r="B66" s="140"/>
+      <c r="C66" s="31">
+        <v>33429</v>
+      </c>
+      <c r="D66" s="132" t="s">
         <v>158</v>
       </c>
-      <c r="B65" s="140"/>
-      <c r="C65" s="181">
-        <v>250000</v>
-      </c>
-      <c r="D65" s="167" t="s">
+    </row>
+    <row r="67" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="139" t="s">
+        <v>159</v>
+      </c>
+      <c r="B67" s="140"/>
+      <c r="C67" s="31">
+        <v>70000</v>
+      </c>
+      <c r="D67" s="132" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="139" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="139" t="s">
-        <v>163</v>
-      </c>
-      <c r="B66" s="140"/>
-      <c r="C66" s="181">
-        <v>33429</v>
-      </c>
-      <c r="D66" s="167" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="139" t="s">
-        <v>165</v>
-      </c>
-      <c r="B67" s="140"/>
-      <c r="C67" s="181">
-        <v>70000</v>
-      </c>
-      <c r="D67" s="167" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="139" t="s">
-        <v>159</v>
-      </c>
       <c r="B68" s="140"/>
-      <c r="C68" s="181">
+      <c r="C68" s="31">
         <v>191330</v>
       </c>
-      <c r="D68" s="167" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D68" s="132" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="18" t="s">
         <v>11</v>
       </c>
@@ -2443,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="27" t="s">
         <v>29</v>
       </c>
@@ -2451,27 +2470,27 @@
       <c r="C70" s="20"/>
       <c r="D70" s="94"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B71" s="5"/>
-      <c r="C71" s="178">
+      <c r="C71" s="111">
         <v>56820.35</v>
       </c>
       <c r="D71" s="99"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B72" s="5"/>
-      <c r="C72" s="178">
+      <c r="C72" s="111">
         <v>142713.93</v>
       </c>
       <c r="D72" s="97"/>
     </row>
-    <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="46" t="s">
         <v>34</v>
       </c>
@@ -2482,69 +2501,72 @@
         <v>199534.28</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="84"/>
       <c r="D74" s="101"/>
     </row>
-    <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="21"/>
-      <c r="C75" s="102"/>
-      <c r="D75" s="103"/>
-    </row>
-    <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="B75" s="178"/>
+      <c r="C75" s="179"/>
+      <c r="D75" s="102">
+        <v>2334921.91</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
-      <c r="C76" s="104"/>
-      <c r="D76" s="105"/>
+      <c r="C76" s="103"/>
+      <c r="D76" s="104"/>
       <c r="E76" s="41"/>
     </row>
-    <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B77" s="10"/>
-      <c r="C77" s="106"/>
-      <c r="D77" s="107">
+      <c r="C77" s="105"/>
+      <c r="D77" s="106">
         <f>(SUM(D29:D75))</f>
-        <v>10317091.089999998</v>
+        <v>11999999.999999998</v>
       </c>
       <c r="E77" s="41"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C78" s="104"/>
-      <c r="D78" s="104"/>
-    </row>
-    <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C79" s="104"/>
-      <c r="D79" s="104"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C78" s="103"/>
+      <c r="D78" s="103"/>
+      <c r="F78" s="180"/>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C79" s="103"/>
+      <c r="D79" s="103"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
         <v>40</v>
       </c>
       <c r="B80" s="12"/>
-      <c r="C80" s="108"/>
-      <c r="D80" s="109"/>
+      <c r="C80" s="107"/>
+      <c r="D80" s="108"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="134"/>
-      <c r="B81" s="135"/>
+      <c r="A81" s="143"/>
+      <c r="B81" s="144"/>
       <c r="C81" s="95"/>
       <c r="D81" s="92"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="134"/>
-      <c r="B82" s="135"/>
+      <c r="A82" s="143"/>
+      <c r="B82" s="144"/>
       <c r="C82" s="95"/>
       <c r="D82" s="92"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="118"/>
-      <c r="B83" s="119"/>
+      <c r="A83" s="116"/>
+      <c r="B83" s="117"/>
       <c r="C83" s="95"/>
       <c r="D83" s="92"/>
     </row>
@@ -2561,16 +2583,16 @@
     <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B87" s="21"/>
       <c r="C87" s="22"/>
-      <c r="D87" s="127"/>
+      <c r="D87" s="125"/>
     </row>
     <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B89" s="10"/>
       <c r="C89" s="4"/>
@@ -2586,7 +2608,7 @@
       </c>
       <c r="B91" s="83">
         <f>D77</f>
-        <v>10317091.089999998</v>
+        <v>11999999.999999998</v>
       </c>
       <c r="C91" s="41"/>
     </row>
@@ -2596,12 +2618,12 @@
       </c>
       <c r="B92" s="83">
         <f>D77-D75</f>
-        <v>10317091.089999998</v>
+        <v>9665078.089999998</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="82" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B93" s="83">
         <f>D89-D87</f>
@@ -2610,7 +2632,7 @@
     </row>
     <row r="94" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="82" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B94" s="83">
         <f>D89</f>
@@ -2620,26 +2642,26 @@
     <row r="95" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="138"/>
-      <c r="B97" s="138"/>
-      <c r="C97" s="138"/>
-      <c r="D97" s="138"/>
+      <c r="A97" s="148"/>
+      <c r="B97" s="148"/>
+      <c r="C97" s="148"/>
+      <c r="D97" s="148"/>
     </row>
     <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="138"/>
-      <c r="B98" s="138"/>
-      <c r="C98" s="138"/>
-      <c r="D98" s="138"/>
+      <c r="A98" s="148"/>
+      <c r="B98" s="148"/>
+      <c r="C98" s="148"/>
+      <c r="D98" s="148"/>
     </row>
     <row r="99" spans="1:4" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="138"/>
-      <c r="B99" s="138"/>
-      <c r="C99" s="138"/>
-      <c r="D99" s="138"/>
+      <c r="A99" s="148"/>
+      <c r="B99" s="148"/>
+      <c r="C99" s="148"/>
+      <c r="D99" s="148"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B101" s="37"/>
     </row>
@@ -2647,128 +2669,130 @@
       <c r="A102" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B102" s="123">
-        <v>157619.68</v>
+      <c r="B102" s="121">
+        <v>-847927.83</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B103" s="38">
         <f>PRORRATEO!H34</f>
-        <v>9253584.9299999997</v>
+        <v>9758198.1199999992</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B104" s="97">
         <f>B120</f>
-        <v>2508209</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B105" s="97"/>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="36" t="s">
+        <v>2145810</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="B105" s="97">
+        <v>-1650000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="B106" s="97">
+        <v>-39552</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B107" s="97">
+        <f>-B92</f>
+        <v>-9665078.089999998</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B106" s="97">
-        <f>-B92</f>
-        <v>-10317091.089999998</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B107" s="97">
+      <c r="B108" s="97">
         <f>-(B93)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="23" t="s">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B108" s="123">
-        <f>SUM(B102:B107)</f>
-        <v>1602322.5200000014</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="39"/>
-      <c r="C109" s="41"/>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="137" t="s">
-        <v>79</v>
-      </c>
-      <c r="B111" s="137"/>
-    </row>
-    <row r="112" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="137"/>
-      <c r="B112" s="137"/>
-    </row>
-    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="110" t="s">
-        <v>167</v>
-      </c>
-      <c r="B113" s="30">
+      <c r="B109" s="121">
+        <f>SUM(B102:B108)</f>
+        <v>-298549.79999999888</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="39"/>
+      <c r="C110" s="41"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="147" t="s">
+        <v>78</v>
+      </c>
+      <c r="B112" s="147"/>
+    </row>
+    <row r="113" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="147"/>
+      <c r="B113" s="147"/>
+    </row>
+    <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="109" t="s">
+        <v>161</v>
+      </c>
+      <c r="B114" s="30">
         <v>562800</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="110" t="s">
-        <v>172</v>
-      </c>
-      <c r="B114" s="30">
-        <v>362399</v>
-      </c>
-    </row>
     <row r="115" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="110" t="s">
-        <v>169</v>
+      <c r="A115" s="109" t="s">
+        <v>163</v>
       </c>
       <c r="B115" s="30">
         <v>400000</v>
       </c>
     </row>
     <row r="116" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="110" t="s">
-        <v>169</v>
+      <c r="A116" s="109" t="s">
+        <v>163</v>
       </c>
       <c r="B116" s="30">
         <v>146000</v>
       </c>
     </row>
     <row r="117" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="110" t="s">
-        <v>170</v>
+      <c r="A117" s="109" t="s">
+        <v>164</v>
       </c>
       <c r="B117" s="30">
         <v>366010</v>
       </c>
     </row>
     <row r="118" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="110" t="s">
-        <v>171</v>
+      <c r="A118" s="109" t="s">
+        <v>165</v>
       </c>
       <c r="B118" s="30">
         <v>545000</v>
       </c>
     </row>
     <row r="119" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="110" t="s">
-        <v>168</v>
-      </c>
-      <c r="B119" s="113">
+      <c r="A119" s="109" t="s">
+        <v>162</v>
+      </c>
+      <c r="B119" s="174">
         <v>126000</v>
       </c>
     </row>
@@ -2776,58 +2800,59 @@
       <c r="A120" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="B120" s="111">
-        <f>SUM(B113:B119)</f>
-        <v>2508209</v>
+      <c r="B120" s="110">
+        <f>SUM(B114:B119)</f>
+        <v>2145810</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L121" s="8"/>
     </row>
     <row r="122" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="136"/>
-      <c r="B122" s="136"/>
-      <c r="C122" s="136"/>
-      <c r="D122" s="136"/>
+      <c r="A122" s="146"/>
+      <c r="B122" s="146"/>
+      <c r="C122" s="146"/>
+      <c r="D122" s="146"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="136"/>
-      <c r="B123" s="136"/>
-      <c r="C123" s="136"/>
-      <c r="D123" s="136"/>
+      <c r="A123" s="146"/>
+      <c r="B123" s="146"/>
+      <c r="C123" s="146"/>
+      <c r="D123" s="146"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="136"/>
-      <c r="B124" s="136"/>
-      <c r="C124" s="136"/>
-      <c r="D124" s="136"/>
+      <c r="A124" s="146"/>
+      <c r="B124" s="146"/>
+      <c r="C124" s="146"/>
+      <c r="D124" s="146"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="136"/>
-      <c r="B125" s="136"/>
-      <c r="C125" s="136"/>
-      <c r="D125" s="136"/>
+      <c r="A125" s="146"/>
+      <c r="B125" s="146"/>
+      <c r="C125" s="146"/>
+      <c r="D125" s="146"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A122:D125"/>
+    <mergeCell ref="A112:B113"/>
+    <mergeCell ref="A97:D99"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A81:B81"/>
     <mergeCell ref="A67:B67"/>
     <mergeCell ref="A14:D17"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A122:D125"/>
-    <mergeCell ref="A111:B112"/>
-    <mergeCell ref="A97:D99"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A81:B81"/>
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="A63:B63"/>
     <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A66:B66"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2863,18 +2888,18 @@
   <sheetData>
     <row r="1" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="141" t="s">
-        <v>125</v>
-      </c>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
+      <c r="B1" s="155" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="155"/>
+      <c r="K1" s="155"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
@@ -2883,41 +2908,41 @@
     </row>
     <row r="2" spans="1:19" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
       <c r="L2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="48">
-        <v>9500000</v>
+      <c r="O2" s="176">
+        <v>12000000</v>
       </c>
       <c r="P2" s="48"/>
       <c r="Q2" s="14"/>
     </row>
     <row r="3" spans="1:19" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="177"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="177"/>
-      <c r="H3" s="177"/>
-      <c r="I3" s="177"/>
-      <c r="J3" s="177"/>
-      <c r="K3" s="177"/>
+      <c r="B3" s="156"/>
+      <c r="C3" s="156"/>
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="156"/>
+      <c r="K3" s="156"/>
       <c r="L3" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
@@ -2925,76 +2950,76 @@
       <c r="P3" s="53"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="143" t="s">
+      <c r="A4" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="145" t="s">
+      <c r="B4" s="171" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="159" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="147" t="s">
+      <c r="D4" s="159" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="147" t="s">
+      <c r="E4" s="159" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="159" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="159" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="159" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="159" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="147" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="147" t="s">
-        <v>90</v>
-      </c>
-      <c r="H4" s="147" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="147" t="s">
+      <c r="J4" s="164" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="154" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" s="152" t="s">
-        <v>48</v>
-      </c>
-      <c r="L4" s="152" t="s">
+      <c r="K4" s="161" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="152" t="s">
-        <v>47</v>
-      </c>
-      <c r="N4" s="157" t="s">
-        <v>88</v>
+      <c r="M4" s="161" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="167" t="s">
+        <v>87</v>
       </c>
       <c r="O4" s="56" t="s">
-        <v>87</v>
-      </c>
-      <c r="P4" s="149" t="s">
         <v>86</v>
       </c>
+      <c r="P4" s="157" t="s">
+        <v>85</v>
+      </c>
       <c r="S4" s="41"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="144"/>
-      <c r="B5" s="146"/>
-      <c r="C5" s="148"/>
-      <c r="D5" s="148"/>
-      <c r="E5" s="151"/>
-      <c r="F5" s="148"/>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="151"/>
-      <c r="J5" s="155"/>
-      <c r="K5" s="153"/>
-      <c r="L5" s="156"/>
-      <c r="M5" s="153"/>
-      <c r="N5" s="158"/>
+      <c r="A5" s="170"/>
+      <c r="B5" s="172"/>
+      <c r="C5" s="163"/>
+      <c r="D5" s="163"/>
+      <c r="E5" s="160"/>
+      <c r="F5" s="163"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="163"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="165"/>
+      <c r="K5" s="162"/>
+      <c r="L5" s="166"/>
+      <c r="M5" s="162"/>
+      <c r="N5" s="168"/>
       <c r="O5" s="54" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/08</v>
       </c>
-      <c r="P5" s="150"/>
+      <c r="P5" s="158"/>
     </row>
     <row r="6" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3004,14 +3029,14 @@
         <v>1</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E6" s="57"/>
       <c r="F6" s="63">
-        <v>1.65</v>
+        <v>4.57</v>
       </c>
       <c r="G6" s="64">
         <v>548400.01</v>
@@ -3026,27 +3051,27 @@
         <v>1.0000000009313226E-2</v>
       </c>
       <c r="K6" s="67">
-        <f>IF(J6&gt;0,J6*3%,0)</f>
-        <v>3.0000000027939676E-4</v>
+        <f>IF(J6&gt;0,J6*2.95%,0)</f>
+        <v>2.9500000027474015E-4</v>
       </c>
       <c r="L6" s="68">
         <f>O$3*F6%</f>
         <v>0</v>
       </c>
       <c r="M6" s="68">
-        <f t="shared" ref="M6:M33" si="0">O$2*F6%</f>
-        <v>156750</v>
+        <f>O$2*F6%</f>
+        <v>548400</v>
       </c>
       <c r="N6" s="69">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="O6" s="70">
-        <f>ROUND(SUM(J6:N6),0) + Q6</f>
-        <v>156750.01</v>
+        <f t="shared" ref="O6:O33" si="0">ROUND(SUM(J6:N6),0) + Q6</f>
+        <v>553400.01</v>
       </c>
       <c r="P6" s="71">
-        <f>ROUND(O6*3%,0) + O6</f>
-        <v>161453.01</v>
+        <f t="shared" ref="P6:P33" si="1">ROUND(O6*3%,0) + O6</f>
+        <v>570002.01</v>
       </c>
       <c r="Q6" s="41">
         <v>0.01</v>
@@ -3060,14 +3085,14 @@
         <v>2</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E7" s="58"/>
       <c r="F7" s="63">
-        <v>1.1599999999999999</v>
+        <v>3.07</v>
       </c>
       <c r="G7" s="64">
         <v>368400.02</v>
@@ -3078,31 +3103,31 @@
       </c>
       <c r="I7" s="66"/>
       <c r="J7" s="67">
-        <f t="shared" ref="J7:J31" si="1">G7-H7</f>
+        <f t="shared" ref="J7:J31" si="2">G7-H7</f>
         <v>-186794.97999999998</v>
       </c>
       <c r="K7" s="67">
-        <f t="shared" ref="K7:K33" si="2">IF(J7&gt;0,J7*3%,0)</f>
+        <f t="shared" ref="K7:K32" si="3">IF(J7&gt;0,J7*2.95%,0)</f>
         <v>0</v>
       </c>
       <c r="L7" s="68">
-        <f t="shared" ref="L7:L33" si="3">O$3*F7%</f>
+        <f t="shared" ref="L7:L33" si="4">O$3*F7%</f>
         <v>0</v>
       </c>
       <c r="M7" s="68">
+        <f t="shared" ref="M6:M33" si="5">O$2*F7%</f>
+        <v>368400</v>
+      </c>
+      <c r="N7" s="69">
+        <v>5000</v>
+      </c>
+      <c r="O7" s="70">
         <f t="shared" si="0"/>
-        <v>110199.99999999999</v>
-      </c>
-      <c r="N7" s="69">
-        <v>0</v>
-      </c>
-      <c r="O7" s="70">
-        <f>ROUND(SUM(J7:N7),0) + Q7</f>
-        <v>-76594.98</v>
+        <v>186605.02</v>
       </c>
       <c r="P7" s="71">
-        <f>ROUND(O7*3%,0) + O7</f>
-        <v>-78892.98</v>
+        <f t="shared" si="1"/>
+        <v>192203.02</v>
       </c>
       <c r="Q7" s="41">
         <f>Q6+0.01</f>
@@ -3118,14 +3143,14 @@
         <v>3</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E8" s="58"/>
       <c r="F8" s="63">
-        <v>1.19</v>
+        <v>4.55</v>
       </c>
       <c r="G8" s="64">
         <v>1719204.03</v>
@@ -3135,34 +3160,32 @@
       </c>
       <c r="I8" s="66"/>
       <c r="J8" s="67">
+        <f t="shared" si="2"/>
+        <v>1719204.03</v>
+      </c>
+      <c r="K8" s="67">
+        <f t="shared" si="3"/>
+        <v>50716.518885000005</v>
+      </c>
+      <c r="L8" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="68">
+        <f t="shared" si="5"/>
+        <v>546000</v>
+      </c>
+      <c r="N8" s="69"/>
+      <c r="O8" s="70">
+        <f t="shared" si="0"/>
+        <v>2315921.0299999998</v>
+      </c>
+      <c r="P8" s="71">
         <f t="shared" si="1"/>
-        <v>1719204.03</v>
-      </c>
-      <c r="K8" s="67">
-        <f t="shared" si="2"/>
-        <v>51576.120900000002</v>
-      </c>
-      <c r="L8" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="68">
-        <f t="shared" si="0"/>
-        <v>113049.99999999999</v>
-      </c>
-      <c r="N8" s="69">
-        <v>0</v>
-      </c>
-      <c r="O8" s="70">
-        <f>ROUND(SUM(J8:N8),0) + Q8</f>
-        <v>1883830.03</v>
-      </c>
-      <c r="P8" s="71">
-        <f>ROUND(O8*3%,0) + O8</f>
-        <v>1940345.03</v>
+        <v>2385399.0299999998</v>
       </c>
       <c r="Q8" s="41">
-        <f t="shared" ref="Q8:Q32" si="4">Q7+0.01</f>
+        <f t="shared" ref="Q8:Q32" si="6">Q7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
@@ -3174,14 +3197,14 @@
         <v>4</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E9" s="58"/>
       <c r="F9" s="63">
-        <v>1.22</v>
+        <v>3.05</v>
       </c>
       <c r="G9" s="64">
         <v>352902.04</v>
@@ -3191,34 +3214,34 @@
       </c>
       <c r="I9" s="66"/>
       <c r="J9" s="67">
+        <f t="shared" si="2"/>
+        <v>-47098</v>
+      </c>
+      <c r="K9" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="68">
+        <f t="shared" si="5"/>
+        <v>366000</v>
+      </c>
+      <c r="N9" s="69">
+        <v>0</v>
+      </c>
+      <c r="O9" s="70">
+        <f t="shared" si="0"/>
+        <v>318902.03999999998</v>
+      </c>
+      <c r="P9" s="71">
         <f t="shared" si="1"/>
-        <v>-47098</v>
-      </c>
-      <c r="K9" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="68">
-        <f t="shared" si="0"/>
-        <v>115899.99999999999</v>
-      </c>
-      <c r="N9" s="69">
-        <v>0</v>
-      </c>
-      <c r="O9" s="70">
-        <f>ROUND(SUM(J9:N9),0) + Q9</f>
-        <v>68802.039999999994</v>
-      </c>
-      <c r="P9" s="71">
-        <f>ROUND(O9*3%,0) + O9</f>
-        <v>70866.039999999994</v>
+        <v>328469.03999999998</v>
       </c>
       <c r="Q9" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.04</v>
       </c>
       <c r="S9" s="41"/>
@@ -3231,14 +3254,14 @@
         <v>5</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E10" s="58"/>
       <c r="F10" s="63">
-        <v>1.67</v>
+        <v>4.55</v>
       </c>
       <c r="G10" s="64">
         <v>545848.05000000005</v>
@@ -3248,34 +3271,34 @@
       </c>
       <c r="I10" s="66"/>
       <c r="J10" s="67">
+        <f t="shared" si="2"/>
+        <v>-4151.9499999999534</v>
+      </c>
+      <c r="K10" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="68">
+        <f t="shared" si="5"/>
+        <v>546000</v>
+      </c>
+      <c r="N10" s="69">
+        <v>0</v>
+      </c>
+      <c r="O10" s="70">
+        <f t="shared" si="0"/>
+        <v>541848.05000000005</v>
+      </c>
+      <c r="P10" s="71">
         <f t="shared" si="1"/>
-        <v>-4151.9499999999534</v>
-      </c>
-      <c r="K10" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="68">
-        <f t="shared" si="0"/>
-        <v>158650</v>
-      </c>
-      <c r="N10" s="69">
-        <v>0</v>
-      </c>
-      <c r="O10" s="70">
-        <f>ROUND(SUM(J10:N10),0) + Q10</f>
-        <v>154498.04999999999</v>
-      </c>
-      <c r="P10" s="71">
-        <f>ROUND(O10*3%,0) + O10</f>
-        <v>159133.04999999999</v>
+        <v>558103.05000000005</v>
       </c>
       <c r="Q10" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.05</v>
       </c>
       <c r="S10" s="41"/>
@@ -3288,14 +3311,14 @@
         <v>6</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E11" s="57"/>
       <c r="F11" s="63">
-        <v>1.71</v>
+        <v>3.05</v>
       </c>
       <c r="G11" s="64">
         <v>366000.06</v>
@@ -3306,34 +3329,34 @@
       </c>
       <c r="I11" s="66"/>
       <c r="J11" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="68">
+        <f t="shared" si="5"/>
+        <v>366000</v>
+      </c>
+      <c r="N11" s="69">
+        <v>5000</v>
+      </c>
+      <c r="O11" s="70">
+        <f t="shared" si="0"/>
+        <v>371000.06</v>
+      </c>
+      <c r="P11" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="68">
-        <f t="shared" si="0"/>
-        <v>162450</v>
-      </c>
-      <c r="N11" s="69">
-        <v>0</v>
-      </c>
-      <c r="O11" s="70">
-        <f>ROUND(SUM(J11:N11),0) + Q11</f>
-        <v>162450.06</v>
-      </c>
-      <c r="P11" s="71">
-        <f>ROUND(O11*3%,0) + O11</f>
-        <v>167324.06</v>
+        <v>382130.06</v>
       </c>
       <c r="Q11" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
@@ -3345,14 +3368,14 @@
         <v>7</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E12" s="57"/>
       <c r="F12" s="63">
-        <v>1.1299999999999999</v>
+        <v>4.55</v>
       </c>
       <c r="G12" s="64">
         <v>543639.06999999995</v>
@@ -3362,34 +3385,34 @@
       </c>
       <c r="I12" s="66"/>
       <c r="J12" s="67">
+        <f t="shared" si="2"/>
+        <v>543639.06999999995</v>
+      </c>
+      <c r="K12" s="67">
+        <f t="shared" si="3"/>
+        <v>16037.352564999999</v>
+      </c>
+      <c r="L12" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="68">
+        <f t="shared" si="5"/>
+        <v>546000</v>
+      </c>
+      <c r="N12" s="69">
+        <v>0</v>
+      </c>
+      <c r="O12" s="70">
+        <f t="shared" si="0"/>
+        <v>1105676.07</v>
+      </c>
+      <c r="P12" s="71">
         <f t="shared" si="1"/>
-        <v>543639.06999999995</v>
-      </c>
-      <c r="K12" s="67">
-        <f t="shared" si="2"/>
-        <v>16309.172099999998</v>
-      </c>
-      <c r="L12" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="68">
-        <f t="shared" si="0"/>
-        <v>107350</v>
-      </c>
-      <c r="N12" s="69">
-        <v>0</v>
-      </c>
-      <c r="O12" s="70">
-        <f>ROUND(SUM(J12:N12),0) + Q12</f>
-        <v>667298.06999999995</v>
-      </c>
-      <c r="P12" s="71">
-        <f>ROUND(O12*3%,0) + O12</f>
-        <v>687317.07</v>
+        <v>1138846.07</v>
       </c>
       <c r="Q12" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -3401,14 +3424,14 @@
         <v>8</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D13" s="57" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E13" s="58"/>
       <c r="F13" s="63">
-        <v>1.1299999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="G13" s="64">
         <v>366000.08</v>
@@ -3418,34 +3441,34 @@
       </c>
       <c r="I13" s="66"/>
       <c r="J13" s="67">
+        <f t="shared" si="2"/>
+        <v>366000.08</v>
+      </c>
+      <c r="K13" s="67">
+        <f t="shared" si="3"/>
+        <v>10797.00236</v>
+      </c>
+      <c r="L13" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="68">
+        <f t="shared" si="5"/>
+        <v>366000</v>
+      </c>
+      <c r="N13" s="69">
+        <v>0</v>
+      </c>
+      <c r="O13" s="70">
+        <f t="shared" si="0"/>
+        <v>742797.08</v>
+      </c>
+      <c r="P13" s="71">
         <f t="shared" si="1"/>
-        <v>366000.08</v>
-      </c>
-      <c r="K13" s="67">
-        <f t="shared" si="2"/>
-        <v>10980.002399999999</v>
-      </c>
-      <c r="L13" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="68">
-        <f t="shared" si="0"/>
-        <v>107350</v>
-      </c>
-      <c r="N13" s="69">
-        <v>0</v>
-      </c>
-      <c r="O13" s="70">
-        <f>ROUND(SUM(J13:N13),0) + Q13</f>
-        <v>484330.08</v>
-      </c>
-      <c r="P13" s="71">
-        <f>ROUND(O13*3%,0) + O13</f>
-        <v>498860.08</v>
+        <v>765081.08</v>
       </c>
       <c r="Q13" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
@@ -3457,14 +3480,14 @@
         <v>9</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D14" s="57" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E14" s="58"/>
       <c r="F14" s="63">
-        <v>1.1299999999999999</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="G14" s="64">
         <v>545707.09</v>
@@ -3474,34 +3497,34 @@
       </c>
       <c r="I14" s="66"/>
       <c r="J14" s="67">
+        <f t="shared" si="2"/>
+        <v>545707.09</v>
+      </c>
+      <c r="K14" s="67">
+        <f t="shared" si="3"/>
+        <v>16098.359155</v>
+      </c>
+      <c r="L14" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="68">
+        <f t="shared" si="5"/>
+        <v>547199.99999999988</v>
+      </c>
+      <c r="N14" s="69">
+        <v>0</v>
+      </c>
+      <c r="O14" s="70">
+        <f t="shared" si="0"/>
+        <v>1109005.0900000001</v>
+      </c>
+      <c r="P14" s="71">
         <f t="shared" si="1"/>
-        <v>545707.09</v>
-      </c>
-      <c r="K14" s="67">
-        <f t="shared" si="2"/>
-        <v>16371.212699999998</v>
-      </c>
-      <c r="L14" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="68">
-        <f t="shared" si="0"/>
-        <v>107350</v>
-      </c>
-      <c r="N14" s="69">
-        <v>0</v>
-      </c>
-      <c r="O14" s="70">
-        <f>ROUND(SUM(J14:N14),0) + Q14</f>
-        <v>669428.09</v>
-      </c>
-      <c r="P14" s="71">
-        <f>ROUND(O14*3%,0) + O14</f>
-        <v>689511.09</v>
+        <v>1142275.0900000001</v>
       </c>
       <c r="Q14" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
     </row>
@@ -3513,14 +3536,14 @@
         <v>10</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D15" s="57" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E15" s="58"/>
       <c r="F15" s="63">
-        <v>1.67</v>
+        <v>3.05</v>
       </c>
       <c r="G15" s="64">
         <v>365999.1</v>
@@ -3530,34 +3553,34 @@
       </c>
       <c r="I15" s="66"/>
       <c r="J15" s="67">
+        <f t="shared" si="2"/>
+        <v>-0.90000000002328306</v>
+      </c>
+      <c r="K15" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="68">
+        <f t="shared" si="5"/>
+        <v>366000</v>
+      </c>
+      <c r="N15" s="69">
+        <v>0</v>
+      </c>
+      <c r="O15" s="70">
+        <f t="shared" si="0"/>
+        <v>365999.1</v>
+      </c>
+      <c r="P15" s="71">
         <f t="shared" si="1"/>
-        <v>-0.90000000002328306</v>
-      </c>
-      <c r="K15" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="68">
-        <f t="shared" si="0"/>
-        <v>158650</v>
-      </c>
-      <c r="N15" s="69">
-        <v>0</v>
-      </c>
-      <c r="O15" s="70">
-        <f>ROUND(SUM(J15:N15),0) + Q15</f>
-        <v>158649.1</v>
-      </c>
-      <c r="P15" s="71">
-        <f>ROUND(O15*3%,0) + O15</f>
-        <v>163408.1</v>
+        <v>376979.1</v>
       </c>
       <c r="Q15" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
@@ -3569,14 +3592,14 @@
         <v>11</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" s="57" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E16" s="58"/>
       <c r="F16" s="63">
-        <v>1.71</v>
+        <v>4.55</v>
       </c>
       <c r="G16" s="64">
         <v>546000.11</v>
@@ -3587,34 +3610,34 @@
       </c>
       <c r="I16" s="66"/>
       <c r="J16" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="68">
+        <f t="shared" si="5"/>
+        <v>546000</v>
+      </c>
+      <c r="N16" s="69">
+        <v>0</v>
+      </c>
+      <c r="O16" s="70">
+        <f t="shared" si="0"/>
+        <v>546000.11</v>
+      </c>
+      <c r="P16" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="68">
-        <f t="shared" si="0"/>
-        <v>162450</v>
-      </c>
-      <c r="N16" s="69">
-        <v>0</v>
-      </c>
-      <c r="O16" s="70">
-        <f>ROUND(SUM(J16:N16),0) + Q16</f>
-        <v>162450.10999999999</v>
-      </c>
-      <c r="P16" s="71">
-        <f>ROUND(O16*3%,0) + O16</f>
-        <v>167324.10999999999</v>
+        <v>562380.11</v>
       </c>
       <c r="Q16" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
@@ -3626,14 +3649,14 @@
         <v>12</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E17" s="58"/>
       <c r="F17" s="63">
-        <v>1.1299999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="G17" s="64">
         <v>125926.12</v>
@@ -3643,34 +3666,34 @@
       </c>
       <c r="I17" s="66"/>
       <c r="J17" s="67">
+        <f t="shared" si="2"/>
+        <v>125926.12</v>
+      </c>
+      <c r="K17" s="67">
+        <f t="shared" si="3"/>
+        <v>3714.8205400000002</v>
+      </c>
+      <c r="L17" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="68">
+        <f t="shared" si="5"/>
+        <v>366000</v>
+      </c>
+      <c r="N17" s="69">
+        <v>0</v>
+      </c>
+      <c r="O17" s="70">
+        <f t="shared" si="0"/>
+        <v>495641.12</v>
+      </c>
+      <c r="P17" s="71">
         <f t="shared" si="1"/>
-        <v>125926.12</v>
-      </c>
-      <c r="K17" s="67">
-        <f t="shared" si="2"/>
-        <v>3777.7835999999998</v>
-      </c>
-      <c r="L17" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="68">
-        <f t="shared" si="0"/>
-        <v>107350</v>
-      </c>
-      <c r="N17" s="69">
-        <v>0</v>
-      </c>
-      <c r="O17" s="70">
-        <f>ROUND(SUM(J17:N17),0) + Q17</f>
-        <v>237054.12</v>
-      </c>
-      <c r="P17" s="71">
-        <f>ROUND(O17*3%,0) + O17</f>
-        <v>244166.12</v>
+        <v>510510.12</v>
       </c>
       <c r="Q17" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
@@ -3682,14 +3705,14 @@
         <v>13</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E18" s="58"/>
       <c r="F18" s="63">
-        <v>1.1299999999999999</v>
+        <v>4.55</v>
       </c>
       <c r="G18" s="64">
         <v>546000.13</v>
@@ -3700,34 +3723,34 @@
       </c>
       <c r="I18" s="66"/>
       <c r="J18" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="68">
+        <f t="shared" si="5"/>
+        <v>546000</v>
+      </c>
+      <c r="N18" s="69">
+        <v>0</v>
+      </c>
+      <c r="O18" s="70">
+        <f t="shared" si="0"/>
+        <v>546000.13</v>
+      </c>
+      <c r="P18" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="68">
-        <f t="shared" si="0"/>
-        <v>107350</v>
-      </c>
-      <c r="N18" s="69">
-        <v>0</v>
-      </c>
-      <c r="O18" s="70">
-        <f>ROUND(SUM(J18:N18),0) + Q18</f>
-        <v>107350.13</v>
-      </c>
-      <c r="P18" s="71">
-        <f>ROUND(O18*3%,0) + O18</f>
-        <v>110571.13</v>
+        <v>562380.13</v>
       </c>
       <c r="Q18" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
@@ -3739,14 +3762,14 @@
         <v>14</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D19" s="57" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E19" s="58"/>
       <c r="F19" s="63">
-        <v>1.1299999999999999</v>
+        <v>3.18</v>
       </c>
       <c r="G19" s="64">
         <v>381600.14</v>
@@ -3757,34 +3780,34 @@
       </c>
       <c r="I19" s="66"/>
       <c r="J19" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="68">
+        <f t="shared" si="5"/>
+        <v>381600</v>
+      </c>
+      <c r="N19" s="69">
+        <v>0</v>
+      </c>
+      <c r="O19" s="70">
+        <f t="shared" si="0"/>
+        <v>381600.14</v>
+      </c>
+      <c r="P19" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="68">
-        <f t="shared" si="0"/>
-        <v>107350</v>
-      </c>
-      <c r="N19" s="69">
-        <v>0</v>
-      </c>
-      <c r="O19" s="70">
-        <f>ROUND(SUM(J19:N19),0) + Q19</f>
-        <v>107350.14</v>
-      </c>
-      <c r="P19" s="71">
-        <f>ROUND(O19*3%,0) + O19</f>
-        <v>110571.14</v>
+        <v>393048.14</v>
       </c>
       <c r="Q19" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
@@ -3796,14 +3819,14 @@
         <v>15</v>
       </c>
       <c r="C20" s="57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D20" s="57" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E20" s="58"/>
       <c r="F20" s="63">
-        <v>1.67</v>
+        <v>4.55</v>
       </c>
       <c r="G20" s="64">
         <v>546000.15</v>
@@ -3813,34 +3836,34 @@
       </c>
       <c r="I20" s="66"/>
       <c r="J20" s="67">
+        <f t="shared" si="2"/>
+        <v>-27300</v>
+      </c>
+      <c r="K20" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="68">
+        <f t="shared" si="5"/>
+        <v>546000</v>
+      </c>
+      <c r="N20" s="69">
+        <v>0</v>
+      </c>
+      <c r="O20" s="70">
+        <f t="shared" si="0"/>
+        <v>518700.15</v>
+      </c>
+      <c r="P20" s="71">
         <f t="shared" si="1"/>
-        <v>-27300</v>
-      </c>
-      <c r="K20" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="68">
-        <f t="shared" si="0"/>
-        <v>158650</v>
-      </c>
-      <c r="N20" s="69">
-        <v>0</v>
-      </c>
-      <c r="O20" s="70">
-        <f>ROUND(SUM(J20:N20),0) + Q20</f>
-        <v>131350.15</v>
-      </c>
-      <c r="P20" s="71">
-        <f>ROUND(O20*3%,0) + O20</f>
-        <v>135291.15</v>
+        <v>534261.15</v>
       </c>
       <c r="Q20" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
     </row>
@@ -3852,14 +3875,14 @@
         <v>16</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D21" s="57" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E21" s="57"/>
       <c r="F21" s="63">
-        <v>1.71</v>
+        <v>3.17</v>
       </c>
       <c r="G21" s="64">
         <v>380400.16</v>
@@ -3870,34 +3893,34 @@
       </c>
       <c r="I21" s="66"/>
       <c r="J21" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="68">
+        <f t="shared" si="5"/>
+        <v>380400</v>
+      </c>
+      <c r="N21" s="69">
+        <v>0</v>
+      </c>
+      <c r="O21" s="70">
+        <f t="shared" si="0"/>
+        <v>380400.16</v>
+      </c>
+      <c r="P21" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="68">
-        <f t="shared" si="0"/>
-        <v>162450</v>
-      </c>
-      <c r="N21" s="69">
-        <v>0</v>
-      </c>
-      <c r="O21" s="70">
-        <f>ROUND(SUM(J21:N21),0) + Q21</f>
-        <v>162450.16</v>
-      </c>
-      <c r="P21" s="71">
-        <f>ROUND(O21*3%,0) + O21</f>
-        <v>167324.16</v>
+        <v>391812.16</v>
       </c>
       <c r="Q21" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.16</v>
       </c>
       <c r="S21" s="40"/>
@@ -3910,14 +3933,14 @@
         <v>17</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D22" s="57" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E22" s="58"/>
       <c r="F22" s="63">
-        <v>1.1299999999999999</v>
+        <v>4.55</v>
       </c>
       <c r="G22" s="65">
         <v>546000.17000000004</v>
@@ -3928,34 +3951,34 @@
       </c>
       <c r="I22" s="66"/>
       <c r="J22" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="68">
+        <f t="shared" si="5"/>
+        <v>546000</v>
+      </c>
+      <c r="N22" s="69">
+        <v>0</v>
+      </c>
+      <c r="O22" s="70">
+        <f t="shared" si="0"/>
+        <v>546000.17000000004</v>
+      </c>
+      <c r="P22" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="68">
-        <f t="shared" si="0"/>
-        <v>107350</v>
-      </c>
-      <c r="N22" s="69">
-        <v>0</v>
-      </c>
-      <c r="O22" s="70">
-        <f>ROUND(SUM(J22:N22),0) + Q22</f>
-        <v>107350.17</v>
-      </c>
-      <c r="P22" s="71">
-        <f>ROUND(O22*3%,0) + O22</f>
-        <v>110571.17</v>
+        <v>562380.17000000004</v>
       </c>
       <c r="Q22" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.17</v>
       </c>
     </row>
@@ -3967,14 +3990,14 @@
         <v>18</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D23" s="57" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E23" s="57"/>
       <c r="F23" s="63">
-        <v>1.1299999999999999</v>
+        <v>3.17</v>
       </c>
       <c r="G23" s="64">
         <v>380400.18</v>
@@ -3985,34 +4008,34 @@
       </c>
       <c r="I23" s="66"/>
       <c r="J23" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="68">
+        <f t="shared" si="5"/>
+        <v>380400</v>
+      </c>
+      <c r="N23" s="69">
+        <v>0</v>
+      </c>
+      <c r="O23" s="70">
+        <f t="shared" si="0"/>
+        <v>380400.18</v>
+      </c>
+      <c r="P23" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="68">
-        <f t="shared" si="0"/>
-        <v>107350</v>
-      </c>
-      <c r="N23" s="69">
-        <v>0</v>
-      </c>
-      <c r="O23" s="70">
-        <f>ROUND(SUM(J23:N23),0) + Q23</f>
-        <v>107350.18</v>
-      </c>
-      <c r="P23" s="71">
-        <f>ROUND(O23*3%,0) + O23</f>
-        <v>110571.18</v>
+        <v>391812.18</v>
       </c>
       <c r="Q23" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
@@ -4024,52 +4047,52 @@
         <v>19</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D24" s="57" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E24" s="58"/>
       <c r="F24" s="63">
-        <v>1.1299999999999999</v>
+        <v>4.55</v>
       </c>
       <c r="G24" s="64">
         <v>1438864.19</v>
       </c>
-      <c r="H24" s="184">
-        <f>388251.19+546000.19</f>
-        <v>934251.37999999989</v>
+      <c r="H24" s="173">
+        <f>388251.19+546000.19+465061.19+39552</f>
+        <v>1438864.5699999998</v>
       </c>
       <c r="I24" s="66"/>
       <c r="J24" s="67">
+        <f t="shared" si="2"/>
+        <v>-0.37999999988824129</v>
+      </c>
+      <c r="K24" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="68">
+        <f t="shared" si="5"/>
+        <v>546000</v>
+      </c>
+      <c r="N24" s="69">
+        <v>0</v>
+      </c>
+      <c r="O24" s="70">
+        <f t="shared" si="0"/>
+        <v>546000.18999999994</v>
+      </c>
+      <c r="P24" s="71">
         <f t="shared" si="1"/>
-        <v>504612.81000000006</v>
-      </c>
-      <c r="K24" s="67">
-        <f t="shared" si="2"/>
-        <v>15138.384300000002</v>
-      </c>
-      <c r="L24" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="68">
-        <f t="shared" si="0"/>
-        <v>107350</v>
-      </c>
-      <c r="N24" s="69">
-        <v>0</v>
-      </c>
-      <c r="O24" s="70">
-        <f>ROUND(SUM(J24:N24),0) + Q24</f>
-        <v>627101.18999999994</v>
-      </c>
-      <c r="P24" s="71">
-        <f>ROUND(O24*3%,0) + O24</f>
-        <v>645914.18999999994</v>
+        <v>562380.18999999994</v>
       </c>
       <c r="Q24" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
@@ -4081,14 +4104,14 @@
         <v>20</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D25" s="57" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E25" s="57"/>
       <c r="F25" s="63">
-        <v>1.67</v>
+        <v>3.17</v>
       </c>
       <c r="G25" s="65">
         <v>380400.2</v>
@@ -4099,38 +4122,38 @@
       </c>
       <c r="I25" s="66"/>
       <c r="J25" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="68">
+        <f t="shared" si="5"/>
+        <v>380400</v>
+      </c>
+      <c r="N25" s="69">
+        <v>0</v>
+      </c>
+      <c r="O25" s="70">
+        <f t="shared" si="0"/>
+        <v>380400.2</v>
+      </c>
+      <c r="P25" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="68">
-        <f t="shared" si="0"/>
-        <v>158650</v>
-      </c>
-      <c r="N25" s="69">
-        <v>0</v>
-      </c>
-      <c r="O25" s="70">
-        <f>ROUND(SUM(J25:N25),0) + Q25</f>
-        <v>158650.20000000001</v>
-      </c>
-      <c r="P25" s="71">
-        <f>ROUND(O25*3%,0) + O25</f>
-        <v>163410.20000000001</v>
+        <v>391812.2</v>
       </c>
       <c r="Q25" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.20000000000000004</v>
       </c>
       <c r="S25" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4141,14 +4164,14 @@
         <v>21</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D26" s="57" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E26" s="58"/>
       <c r="F26" s="63">
-        <v>1.71</v>
+        <v>4.55</v>
       </c>
       <c r="G26" s="64">
         <v>546000.21</v>
@@ -4159,34 +4182,34 @@
       </c>
       <c r="I26" s="66"/>
       <c r="J26" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="68">
+        <f t="shared" si="5"/>
+        <v>546000</v>
+      </c>
+      <c r="N26" s="69">
+        <v>0</v>
+      </c>
+      <c r="O26" s="70">
+        <f t="shared" si="0"/>
+        <v>546000.21</v>
+      </c>
+      <c r="P26" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="68">
-        <f t="shared" si="0"/>
-        <v>162450</v>
-      </c>
-      <c r="N26" s="69">
-        <v>0</v>
-      </c>
-      <c r="O26" s="70">
-        <f>ROUND(SUM(J26:N26),0) + Q26</f>
-        <v>162450.21</v>
-      </c>
-      <c r="P26" s="71">
-        <f>ROUND(O26*3%,0) + O26</f>
-        <v>167324.21</v>
+        <v>562380.21</v>
       </c>
       <c r="Q26" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
@@ -4198,14 +4221,14 @@
         <v>22</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D27" s="57" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E27" s="58"/>
       <c r="F27" s="63">
-        <v>1.1299999999999999</v>
+        <v>3.17</v>
       </c>
       <c r="G27" s="64">
         <v>-1470.22</v>
@@ -4215,34 +4238,34 @@
       </c>
       <c r="I27" s="66"/>
       <c r="J27" s="67">
+        <f t="shared" si="2"/>
+        <v>-1470.22</v>
+      </c>
+      <c r="K27" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="68">
+        <f t="shared" si="5"/>
+        <v>380400</v>
+      </c>
+      <c r="N27" s="69">
+        <v>0</v>
+      </c>
+      <c r="O27" s="70">
+        <f t="shared" si="0"/>
+        <v>378930.22</v>
+      </c>
+      <c r="P27" s="71">
         <f t="shared" si="1"/>
-        <v>-1470.22</v>
-      </c>
-      <c r="K27" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M27" s="68">
-        <f t="shared" si="0"/>
-        <v>107350</v>
-      </c>
-      <c r="N27" s="69">
-        <v>0</v>
-      </c>
-      <c r="O27" s="70">
-        <f>ROUND(SUM(J27:N27),0) + Q27</f>
-        <v>105880.22</v>
-      </c>
-      <c r="P27" s="71">
-        <f>ROUND(O27*3%,0) + O27</f>
-        <v>109056.22</v>
+        <v>390298.22</v>
       </c>
       <c r="Q27" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
@@ -4254,14 +4277,14 @@
         <v>23</v>
       </c>
       <c r="C28" s="57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D28" s="57" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E28" s="58"/>
       <c r="F28" s="63">
-        <v>1.1299999999999999</v>
+        <v>4.66</v>
       </c>
       <c r="G28" s="64">
         <v>486837.23</v>
@@ -4272,34 +4295,34 @@
       </c>
       <c r="I28" s="66"/>
       <c r="J28" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="68">
+        <f t="shared" si="5"/>
+        <v>559200</v>
+      </c>
+      <c r="N28" s="69">
+        <v>0</v>
+      </c>
+      <c r="O28" s="70">
+        <f t="shared" si="0"/>
+        <v>559200.23</v>
+      </c>
+      <c r="P28" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M28" s="68">
-        <f t="shared" si="0"/>
-        <v>107350</v>
-      </c>
-      <c r="N28" s="69">
-        <v>0</v>
-      </c>
-      <c r="O28" s="70">
-        <f>ROUND(SUM(J28:N28),0) + Q28</f>
-        <v>107350.23</v>
-      </c>
-      <c r="P28" s="71">
-        <f>ROUND(O28*3%,0) + O28</f>
-        <v>110571.23</v>
+        <v>575976.23</v>
       </c>
       <c r="Q28" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
@@ -4311,14 +4334,14 @@
         <v>24</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D29" s="57" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E29" s="58"/>
       <c r="F29" s="63">
-        <v>1.1299999999999999</v>
+        <v>3.21</v>
       </c>
       <c r="G29" s="64">
         <v>385200.24</v>
@@ -4329,34 +4352,34 @@
       </c>
       <c r="I29" s="66"/>
       <c r="J29" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="68">
+        <f t="shared" si="5"/>
+        <v>385199.99999999994</v>
+      </c>
+      <c r="N29" s="69">
+        <v>0</v>
+      </c>
+      <c r="O29" s="70">
+        <f t="shared" si="0"/>
+        <v>385200.24</v>
+      </c>
+      <c r="P29" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="68">
-        <f t="shared" si="0"/>
-        <v>107350</v>
-      </c>
-      <c r="N29" s="69">
-        <v>0</v>
-      </c>
-      <c r="O29" s="70">
-        <f>ROUND(SUM(J29:N29),0) + Q29</f>
-        <v>107350.24</v>
-      </c>
-      <c r="P29" s="71">
-        <f>ROUND(O29*3%,0) + O29</f>
-        <v>110571.24</v>
+        <v>396756.24</v>
       </c>
       <c r="Q29" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
@@ -4368,14 +4391,14 @@
         <v>25</v>
       </c>
       <c r="C30" s="57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D30" s="57" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E30" s="57"/>
       <c r="F30" s="63">
-        <v>1.67</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="G30" s="64">
         <v>562800.25</v>
@@ -4385,34 +4408,34 @@
       </c>
       <c r="I30" s="66"/>
       <c r="J30" s="67">
+        <f t="shared" si="2"/>
+        <v>562800.25</v>
+      </c>
+      <c r="K30" s="67">
+        <f t="shared" si="3"/>
+        <v>16602.607375</v>
+      </c>
+      <c r="L30" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="68">
+        <f t="shared" si="5"/>
+        <v>562800</v>
+      </c>
+      <c r="N30" s="69">
+        <v>0</v>
+      </c>
+      <c r="O30" s="70">
+        <f t="shared" si="0"/>
+        <v>1142203.25</v>
+      </c>
+      <c r="P30" s="71">
         <f t="shared" si="1"/>
-        <v>562800.25</v>
-      </c>
-      <c r="K30" s="67">
-        <f t="shared" si="2"/>
-        <v>16884.0075</v>
-      </c>
-      <c r="L30" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M30" s="68">
-        <f t="shared" si="0"/>
-        <v>158650</v>
-      </c>
-      <c r="N30" s="69">
-        <v>0</v>
-      </c>
-      <c r="O30" s="70">
-        <f>ROUND(SUM(J30:N30),0) + Q30</f>
-        <v>738334.25</v>
-      </c>
-      <c r="P30" s="71">
-        <f>ROUND(O30*3%,0) + O30</f>
-        <v>760484.25</v>
+        <v>1176469.25</v>
       </c>
       <c r="Q30" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
@@ -4424,14 +4447,14 @@
         <v>26</v>
       </c>
       <c r="C31" s="57" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D31" s="57" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E31" s="57"/>
       <c r="F31" s="63">
-        <v>1.71</v>
+        <v>3.02</v>
       </c>
       <c r="G31" s="64">
         <v>362399.26</v>
@@ -4442,37 +4465,40 @@
       </c>
       <c r="I31" s="66"/>
       <c r="J31" s="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="67">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L31" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="68">
+        <f t="shared" si="5"/>
+        <v>362400</v>
+      </c>
+      <c r="N31" s="69">
+        <v>0</v>
+      </c>
+      <c r="O31" s="70">
+        <f t="shared" si="0"/>
+        <v>362400.26</v>
+      </c>
+      <c r="P31" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L31" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M31" s="68">
-        <f t="shared" si="0"/>
-        <v>162450</v>
-      </c>
-      <c r="N31" s="69">
-        <v>0</v>
-      </c>
-      <c r="O31" s="70">
-        <f>ROUND(SUM(J31:N31),0) + Q31</f>
-        <v>162450.26</v>
-      </c>
-      <c r="P31" s="71">
-        <f>ROUND(O31*3%,0) + O31</f>
-        <v>167324.26</v>
-      </c>
-      <c r="Q31" s="133">
-        <f t="shared" si="4"/>
+        <v>373272.26</v>
+      </c>
+      <c r="Q31" s="131">
+        <f t="shared" si="6"/>
         <v>0.26000000000000006</v>
       </c>
-      <c r="R31" s="115"/>
+      <c r="R31" s="113"/>
+      <c r="S31" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
@@ -4482,14 +4508,14 @@
         <v>27</v>
       </c>
       <c r="C32" s="57" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D32" s="57" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E32" s="58"/>
       <c r="F32" s="63">
-        <v>1.1299999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="G32" s="64">
         <v>19200.27</v>
@@ -4504,30 +4530,30 @@
         <v>0</v>
       </c>
       <c r="K32" s="67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L32" s="68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M32" s="68">
+        <f>O$2*F32%</f>
+        <v>19200</v>
+      </c>
+      <c r="N32" s="69">
+        <v>0</v>
+      </c>
+      <c r="O32" s="70">
         <f t="shared" si="0"/>
-        <v>107350</v>
-      </c>
-      <c r="N32" s="69">
-        <v>0</v>
-      </c>
-      <c r="O32" s="70">
-        <f>ROUND(SUM(J32:N32),0) + Q32</f>
-        <v>107350.27</v>
+        <v>19200.27</v>
       </c>
       <c r="P32" s="71">
-        <f>ROUND(O32*3%,0) + O32</f>
-        <v>110571.27</v>
+        <f t="shared" si="1"/>
+        <v>19776.27</v>
       </c>
       <c r="Q32" s="41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
@@ -4541,38 +4567,38 @@
       <c r="E33" s="57"/>
       <c r="F33" s="63"/>
       <c r="G33" s="72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H33" s="65" t="str">
-        <f t="shared" ref="H33" si="5">G33</f>
+        <f t="shared" ref="H33" si="7">G33</f>
         <v>162450.31</v>
       </c>
       <c r="I33" s="73"/>
       <c r="J33" s="74" t="e">
-        <f t="shared" ref="J33" si="6">G33-H33</f>
+        <f t="shared" ref="J33" si="8">G33-H33</f>
         <v>#VALUE!</v>
       </c>
       <c r="K33" s="67" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K7:K33" si="9">IF(J33&gt;0,J33*3%,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="L33" s="68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M33" s="75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="76">
+        <v>0</v>
+      </c>
+      <c r="O33" s="70" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N33" s="76">
-        <v>0</v>
-      </c>
-      <c r="O33" s="70" t="e">
-        <f>ROUND(SUM(J33:N33),0) + Q33</f>
         <v>#VALUE!</v>
       </c>
       <c r="P33" s="71" t="e">
-        <f>ROUND(O33*3%,0) + O33</f>
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
       <c r="Q33" s="41"/>
@@ -4584,7 +4610,7 @@
       <c r="E34" s="79"/>
       <c r="F34" s="80">
         <f>SUM(F6:F33)</f>
-        <v>36.809999999999995</v>
+        <v>99.999999999999972</v>
       </c>
       <c r="G34" s="47">
         <f>SUM(G6:G33)</f>
@@ -4592,10 +4618,10 @@
       </c>
       <c r="H34" s="55">
         <f>SUM(H6:H33)</f>
-        <v>9253584.9299999997</v>
+        <v>9758198.1199999992</v>
       </c>
       <c r="I34" s="55">
-        <f t="shared" ref="I34" si="7">SUM(I6:I33)</f>
+        <f t="shared" ref="I34" si="10">SUM(I6:I33)</f>
         <v>0</v>
       </c>
       <c r="J34" s="55"/>
@@ -4606,19 +4632,19 @@
       </c>
       <c r="M34" s="47">
         <f>SUM(M6:M33)</f>
-        <v>3496950</v>
+        <v>12000000</v>
       </c>
       <c r="N34" s="55">
         <f>SUM(N6:N33)</f>
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="O34" s="81">
         <f>SUM(O6:O32)</f>
-        <v>7729062.7800000003</v>
+        <v>15725430.779999999</v>
       </c>
       <c r="P34" s="81">
         <f>SUM(P6:P32)</f>
-        <v>7960941.7800000003</v>
+        <v>16197192.779999999</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4627,91 +4653,96 @@
     </row>
     <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="136"/>
-      <c r="E37" s="136"/>
-      <c r="F37" s="136"/>
-      <c r="G37" s="136"/>
-      <c r="H37" s="136"/>
-      <c r="I37" s="136"/>
-      <c r="J37" s="136"/>
-      <c r="K37" s="136"/>
-      <c r="L37" s="136"/>
-      <c r="M37" s="136"/>
-      <c r="N37" s="136"/>
-      <c r="O37" s="136"/>
+      <c r="D37" s="146"/>
+      <c r="E37" s="146"/>
+      <c r="F37" s="146"/>
+      <c r="G37" s="146"/>
+      <c r="H37" s="146"/>
+      <c r="I37" s="146"/>
+      <c r="J37" s="146"/>
+      <c r="K37" s="146"/>
+      <c r="L37" s="146"/>
+      <c r="M37" s="146"/>
+      <c r="N37" s="146"/>
+      <c r="O37" s="146"/>
     </row>
     <row r="38" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="136"/>
-      <c r="E38" s="136"/>
-      <c r="F38" s="136"/>
-      <c r="G38" s="136"/>
-      <c r="H38" s="136"/>
-      <c r="I38" s="136"/>
-      <c r="J38" s="136"/>
-      <c r="K38" s="136"/>
-      <c r="L38" s="136"/>
-      <c r="M38" s="136"/>
-      <c r="N38" s="136"/>
-      <c r="O38" s="136"/>
+      <c r="D38" s="146"/>
+      <c r="E38" s="146"/>
+      <c r="F38" s="146"/>
+      <c r="G38" s="146"/>
+      <c r="H38" s="146"/>
+      <c r="I38" s="146"/>
+      <c r="J38" s="146"/>
+      <c r="K38" s="146"/>
+      <c r="L38" s="146"/>
+      <c r="M38" s="146"/>
+      <c r="N38" s="146"/>
+      <c r="O38" s="146"/>
     </row>
     <row r="39" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="136"/>
-      <c r="E39" s="136"/>
-      <c r="F39" s="136"/>
-      <c r="G39" s="136"/>
-      <c r="H39" s="136"/>
-      <c r="I39" s="136"/>
-      <c r="J39" s="136"/>
-      <c r="K39" s="136"/>
-      <c r="L39" s="136"/>
-      <c r="M39" s="136"/>
-      <c r="N39" s="136"/>
-      <c r="O39" s="136"/>
+      <c r="D39" s="146"/>
+      <c r="E39" s="146"/>
+      <c r="F39" s="146"/>
+      <c r="G39" s="146"/>
+      <c r="H39" s="146"/>
+      <c r="I39" s="146"/>
+      <c r="J39" s="146"/>
+      <c r="K39" s="146"/>
+      <c r="L39" s="146"/>
+      <c r="M39" s="146"/>
+      <c r="N39" s="146"/>
+      <c r="O39" s="146"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="136"/>
-      <c r="E40" s="136"/>
-      <c r="F40" s="136"/>
-      <c r="G40" s="136"/>
-      <c r="H40" s="136"/>
-      <c r="I40" s="136"/>
-      <c r="J40" s="136"/>
-      <c r="K40" s="136"/>
-      <c r="L40" s="136"/>
-      <c r="M40" s="136"/>
-      <c r="N40" s="136"/>
-      <c r="O40" s="136"/>
+      <c r="D40" s="146"/>
+      <c r="E40" s="146"/>
+      <c r="F40" s="146"/>
+      <c r="G40" s="146"/>
+      <c r="H40" s="146"/>
+      <c r="I40" s="146"/>
+      <c r="J40" s="146"/>
+      <c r="K40" s="146"/>
+      <c r="L40" s="146"/>
+      <c r="M40" s="146"/>
+      <c r="N40" s="146"/>
+      <c r="O40" s="146"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="136"/>
-      <c r="E41" s="136"/>
-      <c r="F41" s="136"/>
-      <c r="G41" s="136"/>
-      <c r="H41" s="136"/>
-      <c r="I41" s="136"/>
-      <c r="J41" s="136"/>
-      <c r="K41" s="136"/>
-      <c r="L41" s="136"/>
-      <c r="M41" s="136"/>
-      <c r="N41" s="136"/>
-      <c r="O41" s="136"/>
+      <c r="D41" s="146"/>
+      <c r="E41" s="146"/>
+      <c r="F41" s="146"/>
+      <c r="G41" s="146"/>
+      <c r="H41" s="146"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="146"/>
+      <c r="K41" s="146"/>
+      <c r="L41" s="146"/>
+      <c r="M41" s="146"/>
+      <c r="N41" s="146"/>
+      <c r="O41" s="146"/>
     </row>
     <row r="42" spans="1:17" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="136"/>
-      <c r="E42" s="136"/>
-      <c r="F42" s="136"/>
-      <c r="G42" s="136"/>
-      <c r="H42" s="136"/>
-      <c r="I42" s="136"/>
-      <c r="J42" s="136"/>
-      <c r="K42" s="136"/>
-      <c r="L42" s="136"/>
-      <c r="M42" s="136"/>
-      <c r="N42" s="136"/>
-      <c r="O42" s="136"/>
+      <c r="D42" s="146"/>
+      <c r="E42" s="146"/>
+      <c r="F42" s="146"/>
+      <c r="G42" s="146"/>
+      <c r="H42" s="146"/>
+      <c r="I42" s="146"/>
+      <c r="J42" s="146"/>
+      <c r="K42" s="146"/>
+      <c r="L42" s="146"/>
+      <c r="M42" s="146"/>
+      <c r="N42" s="146"/>
+      <c r="O42" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="D37:O42"/>
@@ -4724,11 +4755,6 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="N4:N5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
